--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Mensa scolastica (1).xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Mensa scolastica (1).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="145">
   <si>
     <r>
       <t xml:space="preserve">
@@ -109,13 +109,16 @@
     <t>Avviso di pagamento domanda di iscrizione: mancato pagamento</t>
   </si>
   <si>
+    <t>Conferma pagamento sul borsellino</t>
+  </si>
+  <si>
     <t>Pagamento in scadenza sul borsellino</t>
   </si>
   <si>
-    <t>Pagamento non effettuato</t>
+    <t>Richiesta di rinuncia: accolta</t>
   </si>
   <si>
-    <t>Richiesta di rinuncia: accolta</t>
+    <t>Emissione attestazione: spese sostenute</t>
   </si>
   <si>
     <t>Note di compilazione</t>
@@ -291,7 +294,10 @@
     <t>…voglio ricevere un promemoria per i pagamenti scaduti.</t>
   </si>
   <si>
-    <t>…voglio ricevere notifica immediata del mancato addebito sul mio borsellino elettronico.</t>
+    <t>…voglio ricevere una conferma del pagamento effettuato.</t>
+  </si>
+  <si>
+    <t>…voglio ricevere aggiornamenti quando l'ente emette l'attestazione.</t>
   </si>
   <si>
     <r>
@@ -439,7 +445,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>Pagamento non effettuato: ricarica il borsellino</t>
+      <t>Conferma di pagamento</t>
     </r>
   </si>
   <si>
@@ -451,6 +457,17 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t>Hai rinunciato al servizio mensa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>È disponibile l'attestazione delle spese sostenute</t>
     </r>
   </si>
   <si>
@@ -525,7 +542,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> Se hai espresso la preferenza per il tempo pieno, l'iscrizione alla mensa è obbligatorio. 
+      <t xml:space="preserve"> Se hai espresso la preferenza per il tempo pieno, l'iscrizione alla mensa è obbligatoria. 
 Per ulteriori informazioni sul servizio, diete speciali e costi, [visita questa pagina](URL).</t>
     </r>
   </si>
@@ -570,7 +587,59 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> è stata accolta.
+      <t xml:space="preserve"> è stata accolta. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff448844"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>[Se previsto]</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> L'iscrizione sarà valida per il periodo di erogazione del servizio mensa dal </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;gg/mm/aaaa&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> al </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;gg/mm/aaaa&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve">.
 Per ulteriori informazioni, [visita questa pagina](URL).</t>
     </r>
   </si>
@@ -894,9 +963,28 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-Se hai già provveduto a pagare l'avviso ignora questo messaggio.
-Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.</t>
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
+Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
+In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff448844"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>[Se previsto]</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> Per ulteriori informazioni sul calcolo della retta, [visita questo sito](URL).</t>
     </r>
   </si>
   <si>
@@ -1024,7 +1112,24 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">Il termine per il pagamento relativo al servizio mensa per </t>
+      <t xml:space="preserve">Il </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;gg/mm/aaaa&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> è stato effettuato un pagamento sul tuo borsellino elettronico relativo al servizio mensa per </t>
     </r>
     <r>
       <rPr>
@@ -1058,7 +1163,123 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> scadrà il </t>
+      <t xml:space="preserve">.
+Per ulteriori informazioni, [visita questo sito](URL).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve">Il pagamento per </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;causale&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> relativo al servizio mensa per </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;nome&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;cognome&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> è in scadenza. 
+Ricarica il tuo borsellino elettronico con l'importo dovuto entro la data di scadenza. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>Devi pagare:</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;00,00&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> €
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>Entro il:</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -1075,55 +1296,11 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">.
-Ricarica il tuo borsellino elettronico con l'importo dovuto entro la data di scadenza. 
-Per ulteriori informazioni, [visita questo sito](URL).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">Il pagamento automatico per </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;causale&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> non è stato effettuato tramite il borsellino elettronico gestito da </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;ente&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">.
-Ricarica ora per saldare l'importo dovuto. Per farlo, [visita questo sito](URL). 
-Per ulteriori informazioni, [visita questo sito](URL).</t>
+      <t xml:space="preserve">
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
+Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
+In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
   </si>
   <si>
@@ -1135,6 +1312,86 @@
       </rPr>
       <t xml:space="preserve">La tua richiesta di rinuncia al servizio mensa è stata accolta.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve">Dal </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;gg/mm/aaaa&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> è disponibile l'attestazione delle spese sostenute relative al servizio mensa per </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;nome&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;cognome&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> utile ai fini delle detrazioni in sede di dichiarazione dei redditi. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff448844"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>[Solo per messaggi Premium con allegato]</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> Trovi l'attestazione emessa in allegato a questo messaggio.
+Per accedere al portale, [visita questo sito](URL).</t>
     </r>
   </si>
   <si>
@@ -1160,7 +1417,7 @@
     <t>Scopri tutte le agevolazioni</t>
   </si>
   <si>
-    <t>Vedi Avviso</t>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
     <r>
@@ -1187,6 +1444,9 @@
       <t xml:space="preserve">
 File allegato al messaggio</t>
     </r>
+  </si>
+  <si>
+    <t>&lt;documento di attestazione&gt;</t>
   </si>
   <si>
     <r>
@@ -1220,7 +1480,13 @@
     <t>Tutti i genitori/tutori che hanno responsabilità genitoriale di un minore regolarmente iscritto.</t>
   </si>
   <si>
+    <t>Tutti i genitori/tutori che hanno responsabilità genitoriale di un minore regolarmente iscritto</t>
+  </si>
+  <si>
     <t>I cittadini che hanno presentato richiesta di rinuncia.</t>
+  </si>
+  <si>
+    <t>Tutti i genitori/tutori che hanno sostenuto delle spese per il servizio.</t>
   </si>
   <si>
     <r>
@@ -1266,10 +1532,13 @@
     <t>Quando il pagamento non è stato effettuato entro il termine.</t>
   </si>
   <si>
+    <t>Quando il pagamento per la retta è stato effettuato.</t>
+  </si>
+  <si>
     <t>Quando il pagamento per la retta è prossimo alla scadenza.</t>
   </si>
   <si>
-    <t>Quando il pagamento di una retta non è stato effettuato.</t>
+    <t>Quando l'ente emette l'attestazione.</t>
   </si>
   <si>
     <r>
@@ -1851,16 +2120,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="15" width="35" customWidth="1"/>
+    <col min="2" max="16" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>9</v>
@@ -1904,475 +2173,508 @@
       <c r="O1" s="33" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P1" s="33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="K2" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="L2" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="M2" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="O2" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="P2" s="34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="I3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="J3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="N3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="O3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="P3" s="34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="K4" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="L4" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="N4" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="O4" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="P4" s="33" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="K5" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="M5" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="N5" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="O5" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="P5" s="34" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="K6" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="L6" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="N6" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="O6" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="P6" s="34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="H2" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="K2" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="L2" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="M2" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="N2" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="O2" s="34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="I3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="J3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="K3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="L3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="M3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="N3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="O3" s="34" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="J4" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="K4" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="L4" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="M4" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="N4" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="O4" s="33" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="H5" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="I5" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="J5" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="K5" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="L5" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="M5" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="N5" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="O5" s="34" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="J6" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="K6" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="L6" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="M6" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="N6" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="O6" s="34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>64</v>
-      </c>
       <c r="C7" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I7" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J7" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K7" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L7" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M7" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N7" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O7" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>107</v>
-      </c>
       <c r="C8" s="34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L8" s="34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" s="34" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="J9" s="34" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K9" s="34" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L9" s="34" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="M9" s="34" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="N9" s="34" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="O9" s="34" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9" s="34" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="J10" s="34" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="L10" s="34" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="M10" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="O10" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="N10" s="34" t="s">
-        <v>132</v>
+      <c r="P10" s="34" t="s">
+        <v>140</v>
       </c>
-      <c r="O10" s="34" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="J11" s="34" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="K11" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O11" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="P11" s="34" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2399,7 +2701,7 @@
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
@@ -2429,10 +2731,10 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
@@ -2462,10 +2764,10 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -2495,10 +2797,10 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
@@ -2528,10 +2830,10 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -2561,13 +2863,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="22"/>
@@ -2596,10 +2898,10 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
@@ -2629,13 +2931,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
@@ -2664,13 +2966,13 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="26"/>
@@ -2699,10 +3001,10 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
@@ -2732,10 +3034,10 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
@@ -2765,10 +3067,10 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
@@ -2798,10 +3100,10 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
@@ -2831,10 +3133,10 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
@@ -2864,10 +3166,10 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
@@ -2897,10 +3199,10 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
@@ -2930,10 +3232,10 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
@@ -2963,10 +3265,10 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C18" s="29"/>
       <c r="D18" s="29"/>
@@ -2996,10 +3298,10 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C19" s="22"/>
       <c r="D19" s="22"/>
@@ -3029,7 +3331,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="30"/>
@@ -31559,7 +31861,9 @@
     </row>
     <row r="27" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
-      <c r="B27" s="10"/>
+      <c r="B27" s="11" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="28" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
@@ -31742,8 +32046,9 @@
     <hyperlink ref="B24" r:id="rId13" tooltip="Vai al template del messaggio" location="#'Template messaggi'!M1"/>
     <hyperlink ref="B25" r:id="rId14" tooltip="Vai al template del messaggio" location="#'Template messaggi'!N1"/>
     <hyperlink ref="B26" r:id="rId15" tooltip="Vai al template del messaggio" location="#'Template messaggi'!O1"/>
+    <hyperlink ref="B27" r:id="rId16" tooltip="Vai al template del messaggio" location="#'Template messaggi'!P1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId16"/>
+  <drawing r:id="rId17"/>
 </worksheet>
 </file>